--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,31 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
-    <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="15" max="15" width="26.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>First name *</v>
+        <v>First name</v>
       </c>
       <c r="B1" t="str">
-        <v>Last name *</v>
+        <v>Last name</v>
       </c>
       <c r="C1" t="str">
         <v>Full name (Arabic)</v>
@@ -462,57 +445,13 @@
       <c r="O1" t="str">
         <v>ESC ID</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Mohammad</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Al-Ahmad</v>
-      </c>
-      <c r="C2" t="str">
-        <v>محمد علي الأحمد</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Ali</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Mohammad Al-Ahmad</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1985-06-15</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiology</v>
-      </c>
-      <c r="I2" t="str">
-        <v>example@email.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>0911234567</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Damascus</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Al-Mojtahed Hospital</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2020-01-01</v>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
+      <c r="P1" t="str">
+        <v>Submitted at</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,9 +449,109 @@
         <v>Submitted at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ibrahim</v>
+      </c>
+      <c r="B2" t="str">
+        <v>sidawi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D2" t="str">
+        <v>mohammad ali</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>male</v>
+      </c>
+      <c r="H2" t="str">
+        <v>cardiac_surgery</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="L2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="N2" t="str">
+        <v>original</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-05-05T18:29:23.690Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ibrahim</v>
+      </c>
+      <c r="B3" t="str">
+        <v>sidawi</v>
+      </c>
+      <c r="C3" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D3" t="str">
+        <v>mohammad ali</v>
+      </c>
+      <c r="E3" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G3" t="str">
+        <v>male</v>
+      </c>
+      <c r="H3" t="str">
+        <v>cardiac_surgery</v>
+      </c>
+      <c r="I3" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J3" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K3" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="L3" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="N3" t="str">
+        <v>original</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v>2026-05-05T18:31:00.770Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,109 +449,9 @@
         <v>Submitted at</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ibrahim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>sidawi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D2" t="str">
-        <v>mohammad ali</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiac_surgery</v>
-      </c>
-      <c r="I2" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="L2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>2026-05-05T18:29:23.690Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ibrahim</v>
-      </c>
-      <c r="B3" t="str">
-        <v>sidawi</v>
-      </c>
-      <c r="C3" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D3" t="str">
-        <v>mohammad ali</v>
-      </c>
-      <c r="E3" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F3" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G3" t="str">
-        <v>male</v>
-      </c>
-      <c r="H3" t="str">
-        <v>cardiac_surgery</v>
-      </c>
-      <c r="I3" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J3" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K3" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="L3" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="M3" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="N3" t="str">
-        <v>original</v>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v>2026-05-05T18:31:00.770Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,9 +449,59 @@
         <v>Submitted at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ibrahim</v>
+      </c>
+      <c r="B2" t="str">
+        <v>sidawi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D2" t="str">
+        <v>mohammad ali</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>male</v>
+      </c>
+      <c r="H2" t="str">
+        <v>cardiac_surgery</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="L2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="N2" t="str">
+        <v>original</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-05-05T18:59:38.076Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,59 +449,9 @@
         <v>Submitted at</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ibrahim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>sidawi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D2" t="str">
-        <v>mohammad ali</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiac_surgery</v>
-      </c>
-      <c r="I2" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="L2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>2026-05-05T18:59:38.076Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,9 +449,59 @@
         <v>Submitted at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ibrahim</v>
+      </c>
+      <c r="B2" t="str">
+        <v>sidawi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D2" t="str">
+        <v>mohammad ali</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>male</v>
+      </c>
+      <c r="H2" t="str">
+        <v>cardiac_surgery</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="L2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="N2" t="str">
+        <v>original</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-05-05T19:41:04.433Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,59 +449,9 @@
         <v>Submitted at</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ibrahim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>sidawi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D2" t="str">
-        <v>mohammad ali</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiac_surgery</v>
-      </c>
-      <c r="I2" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="L2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>2026-05-05T19:41:04.433Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,9 +449,59 @@
         <v>Submitted at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ibrahim</v>
+      </c>
+      <c r="B2" t="str">
+        <v>sidawi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D2" t="str">
+        <v>mohammad ali</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>male</v>
+      </c>
+      <c r="H2" t="str">
+        <v>cardiac_surgery</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="L2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="N2" t="str">
+        <v>original</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-05-05T19:57:27.633Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -475,19 +475,19 @@
         <v>cardiac_surgery</v>
       </c>
       <c r="I2" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v>+963933706403</v>
       </c>
       <c r="K2" t="str">
-        <v>damascus</v>
+        <v>admascus</v>
       </c>
       <c r="L2" t="str">
         <v>damascus</v>
       </c>
       <c r="M2" t="str">
-        <v>2025-09-05</v>
+        <v>2025-10-01</v>
       </c>
       <c r="N2" t="str">
         <v>original</v>
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-05-05T19:57:27.633Z</v>
+        <v>2026-05-05T20:50:41.568Z</v>
       </c>
     </row>
   </sheetData>

--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-05-05T20:50:41.568Z</v>
+        <v>2026-05-05T21:07:26.271Z</v>
       </c>
     </row>
   </sheetData>

--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,59 +449,9 @@
         <v>Submitted at</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ibrahim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>sidawi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D2" t="str">
-        <v>mohammad ali</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiac_surgery</v>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K2" t="str">
-        <v>admascus</v>
-      </c>
-      <c r="L2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2025-10-01</v>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>2026-05-05T21:07:26.271Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,9 +449,59 @@
         <v>Submitted at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ibrahim</v>
+      </c>
+      <c r="B2" t="str">
+        <v>sidawi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D2" t="str">
+        <v>mohammad ali</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>male</v>
+      </c>
+      <c r="H2" t="str">
+        <v>cardiac_surgery</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K2" t="str">
+        <v>admascus</v>
+      </c>
+      <c r="L2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N2" t="str">
+        <v>original</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-05-06T17:15:22.912Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-05-06T17:15:22.912Z</v>
+        <v>2026-05-06T17:27:30.728Z</v>
       </c>
     </row>
   </sheetData>

--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-05-06T17:27:30.728Z</v>
+        <v>2026-05-06T17:36:49.242Z</v>
       </c>
     </row>
   </sheetData>

--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -475,19 +475,19 @@
         <v>cardiac_surgery</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>ibrahimsidawi@gmail.com</v>
       </c>
       <c r="J2" t="str">
         <v>+963933706403</v>
       </c>
       <c r="K2" t="str">
-        <v>admascus</v>
+        <v>damascus</v>
       </c>
       <c r="L2" t="str">
         <v>damascus</v>
       </c>
       <c r="M2" t="str">
-        <v>2025-10-01</v>
+        <v/>
       </c>
       <c r="N2" t="str">
         <v>original</v>
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-05-06T17:36:49.242Z</v>
+        <v>2026-05-06T18:19:26.603Z</v>
       </c>
     </row>
   </sheetData>

--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-05-06T18:19:26.603Z</v>
+        <v>2026-05-06T18:32:42.450Z</v>
       </c>
     </row>
   </sheetData>

--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-05-06T18:32:42.450Z</v>
+        <v>2026-05-06T18:38:10.578Z</v>
       </c>
     </row>
   </sheetData>

--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,59 +449,9 @@
         <v>Submitted at</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ibrahim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>sidawi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D2" t="str">
-        <v>mohammad ali</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiac_surgery</v>
-      </c>
-      <c r="I2" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="L2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>2026-05-06T18:38:10.578Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,9 +449,59 @@
         <v>Submitted at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ibrahim</v>
+      </c>
+      <c r="B2" t="str">
+        <v>sidawi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D2" t="str">
+        <v>mohammad ali</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>male</v>
+      </c>
+      <c r="H2" t="str">
+        <v>cardiac_surgery</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="L2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>original</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-05-06T19:01:30.320Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -496,7 +496,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>2026-05-06T19:01:30.320Z</v>
+        <v>2026-05-06T19:12:23.420Z</v>
       </c>
     </row>
   </sheetData>

--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,59 +449,9 @@
         <v>Submitted at</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ibrahim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>sidawi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D2" t="str">
-        <v>mohammad ali</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiac_surgery</v>
-      </c>
-      <c r="I2" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="L2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>2026-05-06T19:12:23.420Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,9 +449,59 @@
         <v>Submitted at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ibrahim</v>
+      </c>
+      <c r="B2" t="str">
+        <v>sidawi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D2" t="str">
+        <v>mohammad ali</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>male</v>
+      </c>
+      <c r="H2" t="str">
+        <v>cardiac_surgery</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="L2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>original</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-05-06T19:43:21.158Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,59 +449,9 @@
         <v>Submitted at</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ibrahim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>sidawi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D2" t="str">
-        <v>mohammad ali</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiac_surgery</v>
-      </c>
-      <c r="I2" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="L2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>2026-05-06T19:43:21.158Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,9 +449,59 @@
         <v>Submitted at</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ibrahim</v>
+      </c>
+      <c r="B2" t="str">
+        <v>sidawi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ابراهيم الصيداوي</v>
+      </c>
+      <c r="D2" t="str">
+        <v>mohammad ali</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ibrahim sidawi</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1978-04-05</v>
+      </c>
+      <c r="G2" t="str">
+        <v>male</v>
+      </c>
+      <c r="H2" t="str">
+        <v>cardiac_surgery</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ibrahimsidawi@gmail.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>+963933706403</v>
+      </c>
+      <c r="K2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="L2" t="str">
+        <v>damascus</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>original</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>2026-05-06T20:18:08.201Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
+++ b/docs/form_by_n8n/SCVA-Members-Template-EN.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,59 +449,9 @@
         <v>Submitted at</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ibrahim</v>
-      </c>
-      <c r="B2" t="str">
-        <v>sidawi</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ابراهيم الصيداوي</v>
-      </c>
-      <c r="D2" t="str">
-        <v>mohammad ali</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ibrahim sidawi</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1978-04-05</v>
-      </c>
-      <c r="G2" t="str">
-        <v>male</v>
-      </c>
-      <c r="H2" t="str">
-        <v>cardiac_surgery</v>
-      </c>
-      <c r="I2" t="str">
-        <v>ibrahimsidawi@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>+963933706403</v>
-      </c>
-      <c r="K2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="L2" t="str">
-        <v>damascus</v>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v>original</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>2026-05-06T20:18:08.201Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
   </ignoredErrors>
 </worksheet>
 </file>